--- a/合同全生命周期管理系统-项目管理套件/06_风险问题与变更/问题与变更管理-20260918-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/06_风险问题与变更/问题与变更管理-20260918-V1.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="11" r:id="R9459c783fb9144ee"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题台账" sheetId="7" r:id="R111e47eef4b9428b"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更台账" sheetId="8" r:id="R25d001aa1c5b4bf8"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待决策事项" sheetId="9" r:id="Rc5b39aea8014487f"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_数据接口" sheetId="10" r:id="R99ff430eb21f472e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="11" r:id="R9459c783fb9144ee"/>
   </x:sheets>
 </x:workbook>
 </file>
